--- a/survey_templates/046_in_flight_meal_options_voting_form--survey_templates.xlsx
+++ b/survey_templates/046_in_flight_meal_options_voting_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'chicken'}</t>
+          <t>chicken</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Chicken'}</t>
+          <t>Chicken</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'beef'}</t>
+          <t>beef</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Beef'}</t>
+          <t>Beef</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'fish'}</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Fish'}</t>
+          <t>Fish</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'salad'}</t>
+          <t>salad</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Salad'}</t>
+          <t>Salad</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'hot_food'}</t>
+          <t>hot_food</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Hot Food'}</t>
+          <t>Hot Food</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'cold_food'}</t>
+          <t>cold_food</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Cold Food'}</t>
+          <t>Cold Food</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'no_preference'}</t>
+          <t>no_preference</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'No Preference'}</t>
+          <t>No Preference</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'on_time'}</t>
+          <t>on_time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'On Time'}</t>
+          <t>On Time</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'delayed'}</t>
+          <t>delayed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Delayed'}</t>
+          <t>Delayed</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'breakfast'}</t>
+          <t>breakfast</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Breakfast'}</t>
+          <t>Breakfast</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'lunch'}</t>
+          <t>lunch</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Lunch'}</t>
+          <t>Lunch</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'dinner'}</t>
+          <t>dinner</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Dinner'}</t>
+          <t>Dinner</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'snack'}</t>
+          <t>snack</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Snack'}</t>
+          <t>Snack</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'breakfast'}</t>
+          <t>breakfast</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Breakfast'}</t>
+          <t>Breakfast</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'lunch'}</t>
+          <t>lunch</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Lunch'}</t>
+          <t>Lunch</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'dinner'}</t>
+          <t>dinner</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Dinner'}</t>
+          <t>Dinner</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'snack'}</t>
+          <t>snack</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Snack'}</t>
+          <t>Snack</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'self-service'}</t>
+          <t>self-service</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Self-Service'}</t>
+          <t>Self-Service</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'onboard'}</t>
+          <t>onboard</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Onboard'}</t>
+          <t>Onboard</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'once'}</t>
+          <t>once</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Once'}</t>
+          <t>Once</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'multiple_times'}</t>
+          <t>multiple_times</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Multiple Times'}</t>
+          <t>Multiple Times</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'hot_food'}</t>
+          <t>hot_food</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Hot Food'}</t>
+          <t>Hot Food</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'cold_food'}</t>
+          <t>cold_food</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Cold Food'}</t>
+          <t>Cold Food</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'no_preference'}</t>
+          <t>no_preference</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'No Preference'}</t>
+          <t>No Preference</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'meat'}</t>
+          <t>meat</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Meat'}</t>
+          <t>Meat</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'fruits'}</t>
+          <t>fruits</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Fruits'}</t>
+          <t>Fruits</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'no_preference'}</t>
+          <t>no_preference</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'No Preference'}</t>
+          <t>No Preference</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'coffee'}</t>
+          <t>coffee</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Coffee'}</t>
+          <t>Coffee</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'tea'}</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Tea'}</t>
+          <t>Tea</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'juice'}</t>
+          <t>juice</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Juice'}</t>
+          <t>Juice</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'no_preference'}</t>
+          <t>no_preference</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'No Preference'}</t>
+          <t>No Preference</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'hot_food'}</t>
+          <t>hot_food</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Hot Food'}</t>
+          <t>Hot Food</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'cold_food'}</t>
+          <t>cold_food</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Cold Food'}</t>
+          <t>Cold Food</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'no_preference'}</t>
+          <t>no_preference</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'No Preference'}</t>
+          <t>No Preference</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'breakfast'}</t>
+          <t>breakfast</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Breakfast'}</t>
+          <t>Breakfast</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'lunch'}</t>
+          <t>lunch</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Lunch'}</t>
+          <t>Lunch</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'dinner'}</t>
+          <t>dinner</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Dinner'}</t>
+          <t>Dinner</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'snack'}</t>
+          <t>snack</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Snack'}</t>
+          <t>Snack</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'on_time'}</t>
+          <t>on_time</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'On Time'}</t>
+          <t>On Time</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'delayed'}</t>
+          <t>delayed</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Delayed'}</t>
+          <t>Delayed</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'breakfast'}</t>
+          <t>breakfast</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Breakfast'}</t>
+          <t>Breakfast</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'lunch'}</t>
+          <t>lunch</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Lunch'}</t>
+          <t>Lunch</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'dinner'}</t>
+          <t>dinner</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Dinner'}</t>
+          <t>Dinner</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'snack'}</t>
+          <t>snack</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Snack'}</t>
+          <t>Snack</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'breakfast'}</t>
+          <t>breakfast</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Breakfast'}</t>
+          <t>Breakfast</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'lunch'}</t>
+          <t>lunch</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Lunch'}</t>
+          <t>Lunch</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'dinner'}</t>
+          <t>dinner</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Dinner'}</t>
+          <t>Dinner</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'snack'}</t>
+          <t>snack</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Snack'}</t>
+          <t>Snack</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
